--- a/altiumik/evangelion_turbo_PCB/evangelion_turbo_PCB.xlsx
+++ b/altiumik/evangelion_turbo_PCB/evangelion_turbo_PCB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\szymo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\altiumik\evangelion_turbo_PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C130E5A-6ABC-4D8F-BD4F-55D6ACD3E4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2255522-860F-4CD4-BA6E-586EC62A2A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{A153B71C-0615-465B-90EA-263B602536D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="157">
   <si>
     <t>Comment</t>
   </si>
@@ -452,42 +452,9 @@
     <t>91k-</t>
   </si>
   <si>
-    <t>330R- B!</t>
-  </si>
-  <si>
-    <t>4.7K- B!</t>
-  </si>
-  <si>
     <t>47K (56k)-</t>
   </si>
   <si>
-    <t>300R-</t>
-  </si>
-  <si>
-    <t>1uF- B!</t>
-  </si>
-  <si>
-    <t>100nF- B!</t>
-  </si>
-  <si>
-    <t>10pF B!</t>
-  </si>
-  <si>
-    <t>22uF (10uF)-</t>
-  </si>
-  <si>
-    <t>10uF 16v-</t>
-  </si>
-  <si>
-    <t>22uF 16V-</t>
-  </si>
-  <si>
-    <t>10uF-</t>
-  </si>
-  <si>
-    <t>Model-</t>
-  </si>
-  <si>
     <t>NOPE-</t>
   </si>
   <si>
@@ -497,9 +464,6 @@
     <t>!</t>
   </si>
   <si>
-    <t>390K -</t>
-  </si>
-  <si>
     <t>BAS5202VH6327XTSA1 !</t>
   </si>
   <si>
@@ -512,7 +476,40 @@
     <t>LED GREEN-</t>
   </si>
   <si>
-    <t>AZ1117CR2-3.3TRG1-</t>
+    <t>300R</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>10uF 16v</t>
+  </si>
+  <si>
+    <t>22uF 16V</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>22uF (10uF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10pF </t>
+  </si>
+  <si>
+    <t>1uF-</t>
+  </si>
+  <si>
+    <t>100nF-</t>
+  </si>
+  <si>
+    <t>4.7K-</t>
+  </si>
+  <si>
+    <t>390K-</t>
+  </si>
+  <si>
+    <t>330R-</t>
   </si>
 </sst>
 </file>
@@ -595,6 +592,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -612,20 +623,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -640,23 +637,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83AF5785-1497-447D-B107-E75B21ED870B}" name="Table1" displayName="Table1" ref="A1:F1048576" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83AF5785-1497-447D-B107-E75B21ED870B}" name="Table1" displayName="Table1" ref="A1:F1048576" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:F1048576" xr:uid="{83AF5785-1497-447D-B107-E75B21ED870B}">
     <filterColumn colId="0">
       <filters blank="1">
         <filter val="!"/>
+        <filter val="10pF"/>
+        <filter val="10uF"/>
+        <filter val="10uF 16v"/>
         <filter val="1N4148WT-7"/>
+        <filter val="2.2uF"/>
+        <filter val="22uF (10uF)"/>
+        <filter val="22uF 16V"/>
+        <filter val="300R"/>
         <filter val="4 PIN"/>
+        <filter val="4.7uF"/>
         <filter val="AP63203WU-7"/>
         <filter val="AT24C02D-MAHM-E"/>
+        <filter val="AZ1117CR2-3.3TRG1"/>
         <filter val="banana_plug"/>
         <filter val="BAS5202VH6327XTSA1 !"/>
-        <filter val="BAV199W-7"/>
         <filter val="Buzzer"/>
         <filter val="DF53-4S-0.6H"/>
         <filter val="EG1271A"/>
         <filter val="LSM6DSV320XTR"/>
         <filter val="MLE-102-01-G-DV"/>
+        <filter val="Model"/>
         <filter val="oled flex 0.96"/>
         <filter val="P mos power"/>
         <filter val="SKRHABE010"/>
@@ -665,22 +671,6 @@
         <filter val="TL8B0336M020C (33uF tantalum cap)"/>
         <filter val="TSOP57438TT1"/>
         <filter val="US3200005Z"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters blank="1">
-        <filter val="banana plug for high current scenarios"/>
-        <filter val="Capacitor Polarised"/>
-        <filter val="Connector"/>
-        <filter val="Crystal or Oscillator"/>
-        <filter val="Diode"/>
-        <filter val="General pourpouse inductor"/>
-        <filter val="General Pourpouse Mosfet"/>
-        <filter val="Integrated Circuit"/>
-        <filter val="Resistor"/>
-        <filter val="Schottky Diode"/>
-        <filter val="Switch"/>
-        <filter val="Zener Diode sod523"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1018,7 +1008,7 @@
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
     <col min="2" max="2" width="41.28515625" customWidth="1"/>
-    <col min="3" max="3" width="57.140625" customWidth="1"/>
+    <col min="3" max="3" width="94.85546875" customWidth="1"/>
     <col min="4" max="6" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1044,7 +1034,7 @@
     </row>
     <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -1064,7 +1054,7 @@
     </row>
     <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -1082,9 +1072,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -1122,9 +1112,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -1162,9 +1152,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
@@ -1182,9 +1172,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
@@ -1202,9 +1192,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -1222,7 +1212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -1242,7 +1232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
@@ -1264,7 +1254,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>30</v>
@@ -1284,7 +1274,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>35</v>
@@ -1302,7 +1292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
@@ -1344,7 +1334,7 @@
     </row>
     <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
@@ -1364,7 +1354,7 @@
     </row>
     <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
@@ -1384,7 +1374,7 @@
     </row>
     <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
@@ -1462,9 +1452,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>63</v>
@@ -1584,7 +1574,7 @@
     </row>
     <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>83</v>
@@ -1624,7 +1614,7 @@
     </row>
     <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>90</v>
@@ -1718,9 +1708,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>105</v>
@@ -1738,9 +1728,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>105</v>
@@ -1780,7 +1770,7 @@
     </row>
     <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>111</v>
@@ -1840,7 +1830,7 @@
     </row>
     <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>111</v>
@@ -1860,7 +1850,7 @@
     </row>
     <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>111</v>
@@ -1900,7 +1890,7 @@
     </row>
     <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>111</v>
@@ -1938,9 +1928,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>111</v>

--- a/altiumik/evangelion_turbo_PCB/evangelion_turbo_PCB.xlsx
+++ b/altiumik/evangelion_turbo_PCB/evangelion_turbo_PCB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\altiumik\evangelion_turbo_PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2255522-860F-4CD4-BA6E-586EC62A2A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C41B43-B3AE-43C9-AF20-E1647DF58279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{A153B71C-0615-465B-90EA-263B602536D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="158">
   <si>
     <t>Comment</t>
   </si>
@@ -510,6 +510,9 @@
   </si>
   <si>
     <t>330R-</t>
+  </si>
+  <si>
+    <t>BOOT0 10K (120R)</t>
   </si>
 </sst>
 </file>
@@ -638,42 +641,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83AF5785-1497-447D-B107-E75B21ED870B}" name="Table1" displayName="Table1" ref="A1:F1048576" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:F1048576" xr:uid="{83AF5785-1497-447D-B107-E75B21ED870B}">
-    <filterColumn colId="0">
-      <filters blank="1">
-        <filter val="!"/>
-        <filter val="10pF"/>
-        <filter val="10uF"/>
-        <filter val="10uF 16v"/>
-        <filter val="1N4148WT-7"/>
-        <filter val="2.2uF"/>
-        <filter val="22uF (10uF)"/>
-        <filter val="22uF 16V"/>
-        <filter val="300R"/>
-        <filter val="4 PIN"/>
-        <filter val="4.7uF"/>
-        <filter val="AP63203WU-7"/>
-        <filter val="AT24C02D-MAHM-E"/>
-        <filter val="AZ1117CR2-3.3TRG1"/>
-        <filter val="banana_plug"/>
-        <filter val="BAS5202VH6327XTSA1 !"/>
-        <filter val="Buzzer"/>
-        <filter val="DF53-4S-0.6H"/>
-        <filter val="EG1271A"/>
-        <filter val="LSM6DSV320XTR"/>
-        <filter val="MLE-102-01-G-DV"/>
-        <filter val="Model"/>
-        <filter val="oled flex 0.96"/>
-        <filter val="P mos power"/>
-        <filter val="SKRHABE010"/>
-        <filter val="STM32H562RIV6"/>
-        <filter val="TCAN1042VDRBTQ1"/>
-        <filter val="TL8B0336M020C (33uF tantalum cap)"/>
-        <filter val="TSOP57438TT1"/>
-        <filter val="US3200005Z"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F1048576" xr:uid="{83AF5785-1497-447D-B107-E75B21ED870B}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{BBB5C088-1480-44E3-8734-DCCF34887FE5}" name="Comment"/>
     <tableColumn id="2" xr3:uid="{3AF5C0CA-24A2-4540-94A0-7A21B68F1F51}" name="Description"/>
@@ -1003,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91AB708A-AF16-4558-90D1-C6F8A64A0552}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -1032,7 +1000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>152</v>
       </c>
@@ -1052,7 +1020,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>153</v>
       </c>
@@ -1132,7 +1100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -1292,7 +1260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
@@ -1332,7 +1300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>142</v>
       </c>
@@ -1352,7 +1320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>143</v>
       </c>
@@ -1372,7 +1340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>144</v>
       </c>
@@ -1572,7 +1540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>138</v>
       </c>
@@ -1612,7 +1580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>139</v>
       </c>
@@ -1748,7 +1716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>132</v>
       </c>
@@ -1768,7 +1736,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>137</v>
       </c>
@@ -1788,7 +1756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>133</v>
       </c>
@@ -1808,7 +1776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>134</v>
       </c>
@@ -1828,7 +1796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>154</v>
       </c>
@@ -1848,7 +1816,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>156</v>
       </c>
@@ -1868,7 +1836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>136</v>
       </c>
@@ -1888,7 +1856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>155</v>
       </c>
@@ -1908,7 +1876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>135</v>
       </c>
@@ -2006,6 +1974,11 @@
       </c>
       <c r="F50" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/altiumik/evangelion_turbo_PCB/evangelion_turbo_PCB.xlsx
+++ b/altiumik/evangelion_turbo_PCB/evangelion_turbo_PCB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\altiumik\evangelion_turbo_PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C41B43-B3AE-43C9-AF20-E1647DF58279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1786FE9C-D6A5-4451-BF4F-1245E1F486A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{A153B71C-0615-465B-90EA-263B602536D6}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{A153B71C-0615-465B-90EA-263B602536D6}"/>
   </bookViews>
   <sheets>
     <sheet name="evangelion_turbo_PCB" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="160">
   <si>
     <t>Comment</t>
   </si>
@@ -77,9 +77,6 @@
     <t>C21, C22</t>
   </si>
   <si>
-    <t>TL8B0336M020C (33uF tantalum cap)</t>
-  </si>
-  <si>
     <t>Capacitor Polarised</t>
   </si>
   <si>
@@ -98,9 +95,6 @@
     <t>C 0805</t>
   </si>
   <si>
-    <t>1000pF / 1nF</t>
-  </si>
-  <si>
     <t>C25A, C25B, C25C, C25D, C70A, C70B, C70C, C70D</t>
   </si>
   <si>
@@ -113,18 +107,12 @@
     <t>C28, C34</t>
   </si>
   <si>
-    <t>2.2uF</t>
-  </si>
-  <si>
     <t>C49</t>
   </si>
   <si>
     <t>C 0603</t>
   </si>
   <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
     <t>C50</t>
   </si>
   <si>
@@ -482,21 +470,6 @@
     <t>Model</t>
   </si>
   <si>
-    <t>10uF 16v</t>
-  </si>
-  <si>
-    <t>22uF 16V</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>22uF (10uF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10pF </t>
-  </si>
-  <si>
     <t>1uF-</t>
   </si>
   <si>
@@ -512,7 +485,40 @@
     <t>330R-</t>
   </si>
   <si>
-    <t>BOOT0 10K (120R)</t>
+    <t>1000pF / 1nF-</t>
+  </si>
+  <si>
+    <t>22uF (10uF)-</t>
+  </si>
+  <si>
+    <t>10pF -</t>
+  </si>
+  <si>
+    <t>10uF-</t>
+  </si>
+  <si>
+    <t>22uF 16V-</t>
+  </si>
+  <si>
+    <t>10uF 16v-</t>
+  </si>
+  <si>
+    <t>2.2uF (1uF + 1uF)-</t>
+  </si>
+  <si>
+    <t>4.7uF-</t>
+  </si>
+  <si>
+    <t>AP63203WU-7-</t>
+  </si>
+  <si>
+    <t>P mos power-</t>
+  </si>
+  <si>
+    <t>TL8B0336M020C (2* 10uF 50v low esr)</t>
+  </si>
+  <si>
+    <t>Switch-</t>
   </si>
 </sst>
 </file>
@@ -971,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91AB708A-AF16-4558-90D1-C6F8A64A0552}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -1002,7 +1008,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -1022,7 +1028,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -1042,7 +1048,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -1062,19 +1068,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1082,16 +1088,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>9</v>
@@ -1102,13 +1108,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -1122,16 +1128,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>9</v>
@@ -1142,16 +1148,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>9</v>
@@ -1162,16 +1168,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
@@ -1182,16 +1188,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>9</v>
@@ -1202,16 +1208,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>27</v>
+        <v>155</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>9</v>
@@ -1222,19 +1228,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F13" s="1">
         <v>2</v>
@@ -1242,19 +1248,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1262,19 +1268,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -1282,19 +1288,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F16" s="1">
         <v>4</v>
@@ -1302,19 +1308,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1">
         <v>2</v>
@@ -1322,19 +1328,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F18" s="1">
         <v>2</v>
@@ -1342,19 +1348,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F19" s="1">
         <v>2</v>
@@ -1362,19 +1368,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F20" s="1">
         <v>13</v>
@@ -1382,19 +1388,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F21" s="1">
         <v>2</v>
@@ -1402,19 +1408,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
@@ -1422,19 +1428,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F23" s="1">
         <v>1</v>
@@ -1442,19 +1448,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
@@ -1462,19 +1468,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
@@ -1482,19 +1488,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F26" s="1">
         <v>1</v>
@@ -1502,19 +1508,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F27" s="1">
         <v>1</v>
@@ -1522,19 +1528,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F28" s="1">
         <v>1</v>
@@ -1542,19 +1548,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F29" s="1">
         <v>2</v>
@@ -1562,19 +1568,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F30" s="1">
         <v>2</v>
@@ -1582,19 +1588,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F31" s="1">
         <v>1</v>
@@ -1602,17 +1608,17 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F32" s="1">
         <v>1</v>
@@ -1620,17 +1626,17 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F33" s="1">
         <v>1</v>
@@ -1638,19 +1644,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F34" s="1">
         <v>3</v>
@@ -1658,19 +1664,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F35" s="1">
         <v>2</v>
@@ -1678,19 +1684,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F36" s="1">
         <v>1</v>
@@ -1698,19 +1704,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F37" s="1">
         <v>1</v>
@@ -1718,19 +1724,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F38" s="1">
         <v>15</v>
@@ -1738,19 +1744,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F39" s="1">
         <v>1</v>
@@ -1758,19 +1764,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F40" s="1">
         <v>10</v>
@@ -1778,19 +1784,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F41" s="1">
         <v>1</v>
@@ -1798,19 +1804,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F42" s="1">
         <v>7</v>
@@ -1818,19 +1824,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F43" s="1">
         <v>4</v>
@@ -1838,19 +1844,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F44" s="1">
         <v>1</v>
@@ -1858,19 +1864,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
@@ -1878,19 +1884,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -1898,19 +1904,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F47" s="1">
         <v>8</v>
@@ -1918,19 +1924,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F48" s="1">
         <v>1</v>
@@ -1938,19 +1944,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="E49" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
@@ -1958,27 +1964,22 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F50" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
